--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\Design-Space-Explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D32BA4-A1C3-4DD1-97A7-90DF3CC34AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99DCBBB-9DCD-4BDD-9692-A2BB1D8AF8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="365">
   <si>
     <t>dimension_id</t>
   </si>
@@ -1107,6 +1107,18 @@
   </si>
   <si>
     <t>A mark is a graphical element that represents a data point. The visual properties of the mark map to data. A mark can also indirectly support data encodings when it functions as a unit within a collection and the data mapping occurs at the collection level.</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/mark.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/collection.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/guide.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/scene.png"</t>
   </si>
 </sst>
 </file>
@@ -2030,7 +2042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -2045,7 +2057,9 @@
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="6" t="s">
+        <v>361</v>
+      </c>
       <c r="H2" s="6"/>
       <c r="I2" s="8"/>
       <c r="J2" s="6"/>
@@ -2056,7 +2070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -2071,7 +2085,9 @@
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>362</v>
+      </c>
       <c r="H3" s="6"/>
       <c r="I3" s="8"/>
       <c r="J3" s="6"/>
@@ -2108,7 +2124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>22</v>
       </c>
@@ -2123,7 +2139,9 @@
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="G5" s="6" t="s">
+        <v>363</v>
+      </c>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
       <c r="J5" s="6"/>
@@ -2160,7 +2178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
@@ -2175,7 +2193,9 @@
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="G7" s="6" t="s">
+        <v>364</v>
+      </c>
       <c r="H7" s="6"/>
       <c r="I7" s="8"/>
       <c r="J7" s="6"/>
